--- a/data/trans_bre/P1409-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1409-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-31,66%</t>
+          <t>-31,48%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,98</t>
+          <t>-0,86; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,15</t>
+          <t>-1,69; 2,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,26</t>
+          <t>-3,71; 0,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 170,8</t>
+          <t>-40,69; 203,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 98,17</t>
+          <t>-44,2; 97,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 7,31</t>
+          <t>-61,1; 11,2</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>-16,88%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,6</t>
+          <t>-0,35; 2,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,98</t>
+          <t>0,48; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,4</t>
+          <t>-3,07; 1,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 215,56</t>
+          <t>-16,92; 205,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 250,38</t>
+          <t>16,82; 244,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 114,08</t>
+          <t>-48,79; 31,17</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,8</t>
+          <t>-0,1; 2,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,07</t>
+          <t>0,75; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,76</t>
+          <t>0,34; 4,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 387,19</t>
+          <t>-13,8; 371,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,43; 450,91</t>
+          <t>21,21; 422,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 120,93</t>
+          <t>5,22; 233,3</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>297,4%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,91</t>
+          <t>-1,15; 1,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,46</t>
+          <t>-0,82; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 25,69</t>
+          <t>1,2; 4,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 100,99</t>
+          <t>-34,48; 95,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 102,55</t>
+          <t>-21,91; 104,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,55; 1120,57</t>
+          <t>23,97; 206,15</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,6</t>
+          <t>0,1; 1,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,28</t>
+          <t>0,64; 2,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 9,9</t>
+          <t>-0,1; 1,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 98,72</t>
+          <t>3,94; 102,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,26; 102,86</t>
+          <t>20,53; 112,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 282,19</t>
+          <t>-2,36; 53,82</t>
         </is>
       </c>
     </row>
